--- a/python_data_analysis/cluster_separation_data_v2.xlsx
+++ b/python_data_analysis/cluster_separation_data_v2.xlsx
@@ -1,74 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\C++\slime_mold_simulation\slime_mold_simulation\python_data_analysis\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{459CA1C1-A82D-44AC-829F-7A93B9A667C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tabelle1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
-  <si>
-    <t>f_max</t>
-  </si>
-  <si>
-    <t>f_max err</t>
-  </si>
-  <si>
-    <t>D_chem</t>
-  </si>
-  <si>
-    <t>lambda_max</t>
-  </si>
-  <si>
-    <t>lambda_max_err</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -87,21 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -367,215 +385,251 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>D_chem</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>f_max</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>f_max err</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>lambda_max</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>lambda_max_err</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>16</v>
       </c>
-      <c r="B2">
-        <v>0.18154000000000001</v>
-      </c>
-      <c r="C2">
-        <v>5.9500000000000004E-3</v>
+      <c r="B2" t="n">
+        <v>0.1755145040253987</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.004492691112386715</v>
       </c>
       <c r="D2">
         <f>(1/B2)</f>
-        <v>5.5084278946788583</v>
+        <v/>
       </c>
       <c r="E2">
         <f>D2*(C2/B2)</f>
-        <v>0.18053952833171319</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>18.53</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.1889209059615388</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.006030042744564729</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
         <v>21.33</v>
       </c>
-      <c r="B3">
+      <c r="B4" t="n">
         <v>0.19225</v>
       </c>
-      <c r="C3">
-        <v>5.9699999999999996E-3</v>
-      </c>
-      <c r="D3">
-        <f t="shared" ref="D3:D11" si="0">(1/B3)</f>
-        <v>5.2015604681404417</v>
-      </c>
-      <c r="E3">
-        <f t="shared" ref="E3:E11" si="1">D3*(C3/B3)</f>
-        <v>0.16152570088321683</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4">
+      <c r="C4" t="n">
+        <v>0.00597</v>
+      </c>
+      <c r="D4">
+        <f>(1/B3)</f>
+        <v/>
+      </c>
+      <c r="E4">
+        <f>D3*(C3/B3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
         <v>26.67</v>
       </c>
-      <c r="B4">
-        <v>0.16053000000000001</v>
-      </c>
-      <c r="C4">
-        <v>5.4799999999999996E-3</v>
-      </c>
-      <c r="D4">
-        <f t="shared" si="0"/>
-        <v>6.2293652276832985</v>
-      </c>
-      <c r="E4">
-        <f t="shared" si="1"/>
-        <v>0.21265135144648648</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5">
+      <c r="B5" t="n">
+        <v>0.16053</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.00548</v>
+      </c>
+      <c r="D5">
+        <f>(1/B4)</f>
+        <v/>
+      </c>
+      <c r="E5">
+        <f>D4*(C4/B4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
         <v>32</v>
       </c>
-      <c r="B5">
-        <v>0.12801999999999999</v>
-      </c>
-      <c r="C5">
-        <v>6.8500000000000002E-3</v>
-      </c>
-      <c r="D5">
-        <f t="shared" si="0"/>
-        <v>7.811279487580066</v>
-      </c>
-      <c r="E5">
-        <f t="shared" si="1"/>
-        <v>0.41796019754666036</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6">
+      <c r="B6" t="n">
+        <v>0.12802</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.00685</v>
+      </c>
+      <c r="D6">
+        <f>(1/B5)</f>
+        <v/>
+      </c>
+      <c r="E6">
+        <f>D5*(C5/B5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>37.33</v>
       </c>
-      <c r="B6">
-        <v>0.13950000000000001</v>
-      </c>
-      <c r="C6">
-        <v>9.7999999999999997E-3</v>
-      </c>
-      <c r="D6">
-        <f t="shared" si="0"/>
-        <v>7.1684587813620064</v>
-      </c>
-      <c r="E6">
-        <f t="shared" si="1"/>
-        <v>0.50359065274084336</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7">
+      <c r="B7" t="n">
+        <v>0.1395</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.0098</v>
+      </c>
+      <c r="D7">
+        <f>(1/B6)</f>
+        <v/>
+      </c>
+      <c r="E7">
+        <f>D6*(C6/B6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
         <v>42.67</v>
       </c>
-      <c r="B7">
-        <v>0.14657000000000001</v>
-      </c>
-      <c r="C7">
-        <v>7.8399999999999997E-3</v>
-      </c>
-      <c r="D7">
-        <f t="shared" si="0"/>
-        <v>6.8226785836119257</v>
-      </c>
-      <c r="E7">
-        <f t="shared" si="1"/>
-        <v>0.36494371355337035</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8">
+      <c r="B8" t="n">
+        <v>0.14657</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.00784</v>
+      </c>
+      <c r="D8">
+        <f>(1/B7)</f>
+        <v/>
+      </c>
+      <c r="E8">
+        <f>D7*(C7/B7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
         <v>48</v>
       </c>
-      <c r="B8">
-        <v>0.13317999999999999</v>
-      </c>
-      <c r="C8">
-        <v>1.052E-2</v>
-      </c>
-      <c r="D8">
-        <f t="shared" si="0"/>
-        <v>7.5086349301696957</v>
-      </c>
-      <c r="E8">
-        <f t="shared" si="1"/>
-        <v>0.59311337637321826</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9">
+      <c r="B9" t="n">
+        <v>0.13318</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.01052</v>
+      </c>
+      <c r="D9">
+        <f>(1/B8)</f>
+        <v/>
+      </c>
+      <c r="E9">
+        <f>D8*(C8/B8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
         <v>53.33</v>
       </c>
-      <c r="B9">
-        <v>0.11806999999999999</v>
-      </c>
-      <c r="C9">
-        <v>6.3E-3</v>
-      </c>
-      <c r="D9">
-        <f t="shared" si="0"/>
-        <v>8.4695519607012795</v>
-      </c>
-      <c r="E9">
-        <f t="shared" si="1"/>
-        <v>0.451919855614619</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10">
+      <c r="B10" t="n">
+        <v>0.11807</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.0063</v>
+      </c>
+      <c r="D10">
+        <f>(1/B9)</f>
+        <v/>
+      </c>
+      <c r="E10">
+        <f>D9*(C9/B9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
         <v>58.67</v>
       </c>
-      <c r="B10">
+      <c r="B11" t="n">
         <v>0.11905</v>
       </c>
-      <c r="C10">
-        <v>1.091E-2</v>
-      </c>
-      <c r="D10">
-        <f t="shared" si="0"/>
-        <v>8.3998320033599327</v>
-      </c>
-      <c r="E10">
-        <f t="shared" si="1"/>
-        <v>0.76977880853974689</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11">
+      <c r="C11" t="n">
+        <v>0.01091</v>
+      </c>
+      <c r="D11">
+        <f>(1/B10)</f>
+        <v/>
+      </c>
+      <c r="E11">
+        <f>D10*(C10/B10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
         <v>64</v>
       </c>
-      <c r="B11">
+      <c r="B12" t="n">
         <v>0.11141</v>
       </c>
-      <c r="C11">
-        <v>1.108E-2</v>
-      </c>
-      <c r="D11">
-        <f t="shared" si="0"/>
-        <v>8.9758549501840061</v>
-      </c>
-      <c r="E11">
-        <f t="shared" si="1"/>
-        <v>0.89267097072110935</v>
+      <c r="C12" t="n">
+        <v>0.01108</v>
+      </c>
+      <c r="D12">
+        <f>(1/B11)</f>
+        <v/>
+      </c>
+      <c r="E12">
+        <f>D11*(C11/B11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>18.53</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.1889209059615388</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.006030042744564729</v>
       </c>
     </row>
   </sheetData>
